--- a/output/pdf_financials_xlsx/USGD.xlsx
+++ b/output/pdf_financials_xlsx/USGD.xlsx
@@ -676,10 +676,10 @@
         <v>-9.581637000000001</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5.355745</v>
+        <v>-5.355745</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.870222</v>
+        <v>-1.870222</v>
       </c>
     </row>
     <row r="17">
@@ -752,10 +752,10 @@
         <v>-9.581637000000001</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.355745</v>
+        <v>-5.355745</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.870222</v>
+        <v>-1.870222</v>
       </c>
     </row>
     <row r="21">
@@ -800,10 +800,10 @@
         <v>-9.581637000000001</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.355745</v>
+        <v>-5.355745</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.870222</v>
+        <v>-1.870222</v>
       </c>
     </row>
     <row r="24">
@@ -882,10 +882,10 @@
         <v>-9.468973</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.477147</v>
+        <v>-5.234343</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.16096</v>
+        <v>-1.579484</v>
       </c>
     </row>
     <row r="28">
@@ -914,10 +914,10 @@
         <v>-8.791312</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.367295</v>
+        <v>-4.344195</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.45371</v>
+        <v>0.713266</v>
       </c>
     </row>
     <row r="30">
@@ -952,10 +952,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.931582</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.002353</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.173973</v>
       </c>
     </row>
     <row r="93">
@@ -2040,10 +2040,10 @@
         <v>-9.581637000000001</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>5.355745</v>
+        <v>-5.355745</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>1.870222</v>
+        <v>-1.870222</v>
       </c>
     </row>
     <row r="100">
@@ -3401,7 +3401,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -3996,7 +4000,11 @@
           <t>Warrants reserve 9</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>1.931582</v>
       </c>
@@ -7554,10 +7562,10 @@
         </is>
       </c>
       <c r="F158" s="5" t="n">
-        <v>5.355745</v>
+        <v>-5.355745</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1.870222</v>
+        <v>-1.870222</v>
       </c>
     </row>
     <row r="159">

--- a/output/pdf_financials_xlsx/USGD.xlsx
+++ b/output/pdf_financials_xlsx/USGD.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.58244</v>
+        <v>9.068844</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.428844</v>
+        <v>3.485523</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.278543</v>
+        <v>15.820792</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.58244</v>
+        <v>-9.068844</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.428844</v>
+        <v>-3.485523</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.278543</v>
+        <v>-15.820792</v>
       </c>
     </row>
     <row r="12">
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.557194</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.670304</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.557194</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.670304</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -2932,7 +2932,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -3686,7 +3690,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.147043</v>
       </c>
@@ -4682,7 +4690,11 @@
           <t>Cash paid for reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5713,7 +5725,11 @@
           <t>Cash paid for reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>-0.006467</v>
       </c>
@@ -5905,7 +5921,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
         <v>-0.557194</v>
       </c>
@@ -7017,17 +7037,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-9.068844</v>
+        <v>9.068844</v>
       </c>
       <c r="F140" s="5" t="n">
         <v>3.485523</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>-15.820792</v>
+        <v>15.820792</v>
       </c>
     </row>
     <row r="141">

--- a/output/pdf_financials_xlsx/USGD.xlsx
+++ b/output/pdf_financials_xlsx/USGD.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.58244</v>
+        <v>1.636481</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.428844</v>
+        <v>1.494712</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.278543</v>
+        <v>1.412932</v>
       </c>
     </row>
     <row r="8">
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.452374</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>2.474742</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.023737</v>
       </c>
     </row>
     <row r="71">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.452374</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>2.474742</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.023737</v>
       </c>
     </row>
     <row r="72">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.452374</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>3.028852</v>
+        <v>0.55411</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.023737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>0.766729</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>0.018628</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>0.030077</v>
       </c>
     </row>
     <row r="79">
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>0.766729</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>0.018628</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>0.030077</v>
       </c>
     </row>
     <row r="80">
@@ -1735,20 +1735,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.03116988463208045</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.05119736206596551</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.00167818408095799</v>
       </c>
     </row>
     <row r="81">
@@ -1822,13 +1816,13 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0.922472</v>
+        <v>0.155743</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.110943</v>
+        <v>0.09231499999999999</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.030077</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -3159,7 +3153,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3250,7 +3248,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3857,7 +3859,11 @@
           <t>Current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.452374</v>
       </c>
@@ -3917,7 +3923,11 @@
           <t>Lease obligations 8</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.766729</v>
       </c>
@@ -6764,7 +6774,11 @@
           <t>Management and directors' fees 12</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -7850,7 +7864,11 @@
           <t>Directors' fees 10</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>0.054041</v>
       </c>
